--- a/data/EVALUACIONES/CAMPO/CAMPO.xlsx
+++ b/data/EVALUACIONES/CAMPO/CAMPO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\CAMPO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDD9E75-E1B7-4219-8CA3-1E8CA236D576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{2FDD9E75-E1B7-4219-8CA3-1E8CA236D576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3347057-C931-427F-9C7D-10C705C6384D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Fecha</t>
   </si>
@@ -88,9 +88,6 @@
   </si>
   <si>
     <t>Jorge_vicaria</t>
-  </si>
-  <si>
-    <t>rodrigo_cueva</t>
   </si>
   <si>
     <t>Tecnica_Sprint</t>
@@ -267,17 +264,6 @@
   </cellStyles>
   <dxfs count="9">
     <dxf>
-      <font>
-        <sz val="10"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="4" tint="0.79998168889431442"/>
@@ -318,6 +304,17 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -388,16 +385,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:G29" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G29" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:G28" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G28" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{B90CC2EA-DED7-4B50-9C01-6648707B7686}" name="Fecha" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{49BFBD1B-88C4-49EF-ACC0-907CF6D29923}" name="Nombre" dataDxfId="5"/>
     <tableColumn id="11" xr3:uid="{2485B2B6-1AA4-4901-8B45-87383DB57039}" name="V_MAX" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{10A89B76-6E25-4687-86FC-402E5875F343}" name="AC_MAX" dataDxfId="0"/>
-    <tableColumn id="13" xr3:uid="{B6A95FF8-2A19-4995-B36D-CAC2D284919B}" name="DEC_MAX" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{6F0B8C04-FF29-4644-9965-73441115C769}" name="Tecnica_Sprint" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{ED7A1510-B4D4-448C-A7B6-385AEFB0314D}" name="Tecnica_COD" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{10A89B76-6E25-4687-86FC-402E5875F343}" name="AC_MAX" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{B6A95FF8-2A19-4995-B36D-CAC2D284919B}" name="DEC_MAX" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{6F0B8C04-FF29-4644-9965-73441115C769}" name="Tecnica_Sprint" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{ED7A1510-B4D4-448C-A7B6-385AEFB0314D}" name="Tecnica_COD" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -700,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -727,10 +724,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="H1" s="3"/>
     </row>
@@ -791,7 +788,7 @@
         <v>46247</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
@@ -817,7 +814,7 @@
         <v>46247</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
@@ -889,7 +886,7 @@
         <v>46247</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
@@ -993,7 +990,7 @@
         <v>46247</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12">
         <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
@@ -1019,7 +1016,7 @@
         <v>46247</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13">
         <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
@@ -1097,7 +1094,7 @@
         <v>46247</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" s="9">
         <v>34.037999999999997</v>
@@ -1143,7 +1140,7 @@
         <v>46247</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="9">
         <v>33.188000000000002</v>
@@ -1235,7 +1232,7 @@
         <v>46247</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="9">
         <v>31.914000000000001</v>
@@ -1258,7 +1255,7 @@
         <v>46247</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23" s="9">
         <v>34.530999999999999</v>
@@ -1281,7 +1278,7 @@
         <v>46247</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="9">
         <v>32.926000000000002</v>
@@ -1327,7 +1324,7 @@
         <v>46247</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="9">
         <v>31.414000000000001</v>
@@ -1368,7 +1365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46247</v>
       </c>
@@ -1389,29 +1386,6 @@
       </c>
       <c r="G28" s="5">
         <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
-        <v>46247</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="9">
-        <v>33.616999999999997</v>
-      </c>
-      <c r="D29" s="9">
-        <v>5.5529999999999999</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-4.8680000000000003</v>
-      </c>
-      <c r="F29" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="G29" s="5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
